--- a/data/trans_orig/IP26C_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP26C_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2007 (tasa de respuesta: 99,43%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2007 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23875</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22298</t>
+          <t>22883</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38796</t>
+          <t>39076</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>114144</t>
+          <t>114303</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>127038</t>
+          <t>126823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129513</t>
+          <t>129244</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141047</t>
+          <t>140774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>249475</t>
+          <t>249195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>265973</t>
+          <t>265388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20919</t>
+          <t>20859</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36175</t>
+          <t>35585</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15337</t>
+          <t>15035</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30067</t>
+          <t>28950</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39631</t>
+          <t>39465</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60120</t>
+          <t>59530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>158366</t>
+          <t>158956</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173622</t>
+          <t>173682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180087</t>
+          <t>181204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>194817</t>
+          <t>195119</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344575</t>
+          <t>345165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>365064</t>
+          <t>365230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17957</t>
+          <t>17942</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10751</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23171</t>
+          <t>22296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21086</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36232</t>
+          <t>35744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>119860</t>
+          <t>119875</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130632</t>
+          <t>130451</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125847</t>
+          <t>126722</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138267</t>
+          <t>138710</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>250603</t>
+          <t>251091</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>265749</t>
+          <t>266930</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16736</t>
+          <t>16537</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32369</t>
+          <t>32513</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23608</t>
+          <t>22647</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30545</t>
+          <t>30104</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51459</t>
+          <t>49761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>176284</t>
+          <t>176140</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>191917</t>
+          <t>192116</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>183521</t>
+          <t>184482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>196719</t>
+          <t>196433</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>364323</t>
+          <t>366021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>385237</t>
+          <t>385678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65248</t>
+          <t>65682</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92607</t>
+          <t>92845</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56136</t>
+          <t>55401</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80860</t>
+          <t>82080</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126605</t>
+          <t>126903</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165722</t>
+          <t>164698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>586422</t>
+          <t>586184</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>613781</t>
+          <t>613347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>635695</t>
+          <t>634475</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>660419</t>
+          <t>661154</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1229862</t>
+          <t>1230886</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1268979</t>
+          <t>1268681</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2012 (tasa de respuesta: 98,9%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2012 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9623</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>21843</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25246</t>
+          <t>24357</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>24255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43267</t>
+          <t>42934</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115901</t>
+          <t>116186</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128406</t>
+          <t>128096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>128808</t>
+          <t>129697</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>142539</t>
+          <t>141979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248815</t>
+          <t>249148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>267658</t>
+          <t>267827</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11183</t>
+          <t>11280</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23297</t>
+          <t>23884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>18980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34046</t>
+          <t>35170</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34119</t>
+          <t>33863</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53774</t>
+          <t>54014</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181225</t>
+          <t>180638</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>193339</t>
+          <t>193242</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>187102</t>
+          <t>185978</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>202222</t>
+          <t>202168</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>371896</t>
+          <t>371656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>391551</t>
+          <t>391807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7649</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22002</t>
+          <t>22460</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>20271</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35275</t>
+          <t>35915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135059</t>
+          <t>135751</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146207</t>
+          <t>146555</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141741</t>
+          <t>141283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153602</t>
+          <t>153320</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>282324</t>
+          <t>281684</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>297109</t>
+          <t>297328</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>20954</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39155</t>
+          <t>38345</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16140</t>
+          <t>15375</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31240</t>
+          <t>29991</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41464</t>
+          <t>41186</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63972</t>
+          <t>63759</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168016</t>
+          <t>168826</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186304</t>
+          <t>186217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>174789</t>
+          <t>176038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>189889</t>
+          <t>190654</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>349228</t>
+          <t>349441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>371736</t>
+          <t>372014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61927</t>
+          <t>61693</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87534</t>
+          <t>87705</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67988</t>
+          <t>68057</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96061</t>
+          <t>96554</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>134359</t>
+          <t>135645</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174051</t>
+          <t>174286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>616043</t>
+          <t>615872</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>641650</t>
+          <t>641884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>648913</t>
+          <t>648420</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>676986</t>
+          <t>676917</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1274500</t>
+          <t>1274265</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1314192</t>
+          <t>1312906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2016 (tasa de respuesta: 99,01%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2016 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13650</t>
+          <t>13581</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18858</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13375</t>
+          <t>13965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28209</t>
+          <t>28001</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118689</t>
+          <t>118758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128481</t>
+          <t>128376</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129218</t>
+          <t>129170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140333</t>
+          <t>140925</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252206</t>
+          <t>252414</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>267040</t>
+          <t>266450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24257</t>
+          <t>24716</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13407</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27035</t>
+          <t>26772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27468</t>
+          <t>28057</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46422</t>
+          <t>46594</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179991</t>
+          <t>179532</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>192610</t>
+          <t>192877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195422</t>
+          <t>195685</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209050</t>
+          <t>209186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>380283</t>
+          <t>380111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>399237</t>
+          <t>398648</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25762</t>
+          <t>24718</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24250</t>
+          <t>23869</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27163</t>
+          <t>27049</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44465</t>
+          <t>44803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128564</t>
+          <t>129608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141634</t>
+          <t>141507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141736</t>
+          <t>142117</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155263</t>
+          <t>154437</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>275847</t>
+          <t>275509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>293149</t>
+          <t>293263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31278</t>
+          <t>30356</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32779</t>
+          <t>32971</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54291</t>
+          <t>54029</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174746</t>
+          <t>175668</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190493</t>
+          <t>190852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173139</t>
+          <t>173666</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188002</t>
+          <t>187613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>353760</t>
+          <t>354022</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>375272</t>
+          <t>375080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53124</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78190</t>
+          <t>78767</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>55483</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83849</t>
+          <t>82556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116934</t>
+          <t>117201</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152569</t>
+          <t>152216</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>618748</t>
+          <t>618171</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>643814</t>
+          <t>643296</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>654697</t>
+          <t>655990</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>682042</t>
+          <t>683063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1282914</t>
+          <t>1283267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1318549</t>
+          <t>1318282</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>9065</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20848</t>
+          <t>20574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12273</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28348</t>
+          <t>28862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>24321</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45047</t>
+          <t>45098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96432</t>
+          <t>96706</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108016</t>
+          <t>108215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112064</t>
+          <t>111550</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128139</t>
+          <t>128709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>212646</t>
+          <t>212595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>233484</t>
+          <t>233372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15407</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30404</t>
+          <t>30728</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23892</t>
+          <t>23278</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44451</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43836</t>
+          <t>45199</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68675</t>
+          <t>67831</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160108</t>
+          <t>159784</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>175105</t>
+          <t>174961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210584</t>
+          <t>211453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>231143</t>
+          <t>231757</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>376873</t>
+          <t>377717</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>401712</t>
+          <t>400349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>5719</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17287</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30548</t>
+          <t>31365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>170917</t>
+          <t>171347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183691</t>
+          <t>183418</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>167572</t>
+          <t>166799</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179110</t>
+          <t>179140</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>343897</t>
+          <t>343080</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>360274</t>
+          <t>360445</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>18401</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>28587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22910</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42366</t>
+          <t>42865</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148345</t>
+          <t>148371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159507</t>
+          <t>159293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152488</t>
+          <t>152651</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167834</t>
+          <t>167591</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>305644</t>
+          <t>305145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>325100</t>
+          <t>324480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47668</t>
+          <t>47650</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74045</t>
+          <t>73478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67496</t>
+          <t>67044</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98738</t>
+          <t>99187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124334</t>
+          <t>123542</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>166277</t>
+          <t>165872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>590105</t>
+          <t>590672</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>616482</t>
+          <t>616500</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>662807</t>
+          <t>662358</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>694049</t>
+          <t>694501</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1259418</t>
+          <t>1259823</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1301361</t>
+          <t>1302153</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP26C_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP26C_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14220</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8936</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21080</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>16361</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11196</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23716</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>11507</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>23114</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,85%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14220</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9479</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21009</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22883</t>
+          <t>23363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39076</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>136033</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>129173</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>141317</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>121658</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>114303</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>126823</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>114905</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>126512</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>88,15%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>91,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>136033</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>129244</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>140774</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,54%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>249195</t>
+          <t>247764</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>265388</t>
+          <t>264908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>150253</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>150253</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>150253</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138019</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138019</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138019</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>150253</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>150253</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>150253</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21401</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15048</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>28604</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>27548</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20859</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>35585</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>20126</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>35057</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>14,16%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>21401</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>15035</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>28950</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39465</t>
+          <t>39444</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59530</t>
+          <t>60427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>188753</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>181550</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>195106</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>166993</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>158956</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>173682</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>159484</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>174415</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>85,84%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>188753</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>181204</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>195119</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,82%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>345165</t>
+          <t>344268</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>365230</t>
+          <t>365251</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210154</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210154</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210154</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>194541</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>194541</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>194541</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210154</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210154</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210154</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15886</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10654</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22124</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,66%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>11693</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7366</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17942</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7449</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17531</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>8,48%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15886</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10308</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22296</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,66%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>20414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35744</t>
+          <t>36150</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>133132</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>126894</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>138364</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,34%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,85%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>126124</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>119875</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>130451</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>120286</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>130368</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>91,52%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,98%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>133132</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>126722</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>138710</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,34%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>251091</t>
+          <t>250685</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>266930</t>
+          <t>266421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149018</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149018</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149018</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149018</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149018</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149018</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16093</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10509</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23135</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>23305</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16537</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>32513</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16566</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>32383</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16093</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10696</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>22647</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49761</t>
+          <t>50041</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>191036</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>183994</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>196620</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>185348</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>176140</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>192116</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>176270</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>192087</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>191036</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>184482</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>196433</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>366021</t>
+          <t>365741</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>385678</t>
+          <t>385992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207129</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207129</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207129</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>208653</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>208653</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>208653</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207129</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207129</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207129</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>67600</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>55776</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>80366</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>78908</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>65682</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>92845</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>65895</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>93971</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>11,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>67600</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>55401</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>82080</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126903</t>
+          <t>129891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164698</t>
+          <t>164954</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>648955</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>636189</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>660779</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,22%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>898</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>600121</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>586184</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>613347</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>585058</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>613134</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>88,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>86,33%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>648955</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>634475</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>661154</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,57%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1230886</t>
+          <t>1230630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1268681</t>
+          <t>1265693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>716555</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>716555</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>716555</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>679029</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>679029</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>679029</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1077</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>716555</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>716555</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>716555</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17602</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12041</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25327</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,43%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9933</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21843</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9541</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>22043</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10,99%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17602</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12075</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24357</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,43%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24255</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42934</t>
+          <t>41769</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>136452</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>128727</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>142013</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>122858</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>116186</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>128096</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>115986</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>128488</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>89,01%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>136452</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>129697</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>141979</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,57%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>249148</t>
+          <t>250313</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>267827</t>
+          <t>267839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>154054</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154054</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>154054</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138029</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138029</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138029</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>154054</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154054</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154054</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26361</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19464</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>35447</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16797</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11280</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>23884</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11298</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24343</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,21%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>5,52%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26361</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18980</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>35170</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33863</t>
+          <t>34356</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54014</t>
+          <t>54363</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>194787</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>185701</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>201684</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,97%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>291</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>187725</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>180638</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>193242</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>180179</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,79%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>88,1%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>94,48%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>194787</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>185978</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>202168</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,08%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>84,1%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>91,42%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>572</t>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>371656</t>
+          <t>371307</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>391807</t>
+          <t>391314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221148</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221148</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221148</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>316</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>204522</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>204522</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>204522</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221148</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221148</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221148</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15135</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10186</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21956</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,41%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>11995</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7301</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18105</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7573</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18045</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,8%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15135</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10423</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22460</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20271</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35915</t>
+          <t>35974</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148608</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>141787</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>153557</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,59%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>141861</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>135751</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>146555</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>135811</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>146283</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,2%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148608</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>141283</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>153320</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,76%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>281684</t>
+          <t>281625</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>297328</t>
+          <t>297606</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>163743</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>163743</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>163743</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>153856</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>153856</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>153856</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>163743</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>163743</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>163743</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22185</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15738</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30007</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>29256</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20954</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>38345</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>21135</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>38593</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>14,12%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>22185</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15375</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29991</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,77%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41186</t>
+          <t>40425</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63759</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>183844</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>176022</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>190291</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>85,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>177915</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>168826</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>186217</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>168578</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>186036</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>85,88%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>183844</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>176038</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>190654</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>349441</t>
+          <t>349234</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>372014</t>
+          <t>372775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206029</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206029</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206029</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207171</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207171</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207171</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206029</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206029</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206029</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>81283</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>68407</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>96745</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,99%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>73218</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>61693</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>87705</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>60202</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>86826</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>10,41%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>81283</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>68057</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>96554</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>135645</t>
+          <t>136374</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174286</t>
+          <t>174848</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>663691</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>648229</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>676567</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>87,01%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>912</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>630359</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>615872</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>641884</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>616751</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>643375</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>89,59%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>663691</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>648420</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>676917</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>89,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1274265</t>
+          <t>1273703</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1312906</t>
+          <t>1312177</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744974</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744974</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744974</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1014</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>703577</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>703577</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>703577</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744974</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744974</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744974</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12191</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7119</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18829</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7924</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3963</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13581</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4233</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14064</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,99%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,26%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12191</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7151</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18906</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13965</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28001</t>
+          <t>28289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>135885</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>129247</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>140957</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,77%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>124415</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>118758</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>128376</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>118275</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>128106</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,01%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>135885</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>129170</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>140925</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,77%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252414</t>
+          <t>252126</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>266450</t>
+          <t>266492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>132339</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>132339</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>132339</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19063</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13231</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26488</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16949</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11371</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24716</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11763</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24770</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,3%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,1%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>19063</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>13271</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>26772</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28057</t>
+          <t>28101</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46594</t>
+          <t>46095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>203394</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>195969</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>209226</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,05%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>187299</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>179532</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>192877</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>179478</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>192485</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,7%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,43%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>203394</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>195685</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>209186</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,43%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>380111</t>
+          <t>380610</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>398648</t>
+          <t>398604</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -5191,52 +5191,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>222457</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>222457</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>222457</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>204248</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>204248</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>204248</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>222457</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>222457</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>222457</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16826</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11527</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24774</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,93%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>18274</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12819</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24718</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12832</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>25522</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,84%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>8,31%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>16826</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11549</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>23869</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27049</t>
+          <t>27020</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44803</t>
+          <t>44933</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -5416,74 +5416,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149160</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>141212</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>154459</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,07%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>136052</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>129608</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>141507</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>128804</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>141494</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,16%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,98%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>83,46%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>91,69%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149160</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>142117</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>154437</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,86%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>85,62%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>449</t>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>275509</t>
+          <t>275379</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>293263</t>
+          <t>293292</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165986</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165986</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165986</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154326</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154326</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154326</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165986</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165986</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165986</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20572</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14326</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27459</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>22391</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15172</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>30356</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15770</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>31567</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,87%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,73%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20572</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>14414</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>28361</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32971</t>
+          <t>32351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54029</t>
+          <t>53964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>181455</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>174568</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>187701</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>86,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>249</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>183633</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>175668</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>190852</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>174457</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>190254</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,13%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,27%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>181455</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>173666</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>187613</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,82%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>354022</t>
+          <t>354087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>375080</t>
+          <t>375700</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202027</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202027</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202027</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206024</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206024</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206024</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202027</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202027</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202027</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5994,67 +5994,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>68652</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>56425</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>82320</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>65539</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>53642</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>78767</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>52926</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>78613</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>68652</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>55483</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>82556</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117201</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152216</t>
+          <t>153372</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>669894</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>656226</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>682121</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,7%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,85%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>952</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>631399</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>618171</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>643296</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>618325</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>644012</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>88,7%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>669894</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>655990</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>683063</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1283267</t>
+          <t>1282111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1318282</t>
+          <t>1318400</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1056</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>738546</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>738546</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>738546</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1049</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>696938</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>696938</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>696938</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1056</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>738546</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>738546</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>738546</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>12184</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20574</t>
+          <t>28494</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28862</t>
+          <t>20554</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>33380</t>
+          <t>33206</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>23897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45098</t>
+          <t>43653</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>106929</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>97412</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>113722</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>84,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,37%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>90,32%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>102973</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>96706</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>108215</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>87,8%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,46%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,27%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>121339</t>
+          <t>106842</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111550</t>
+          <t>100517</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128709</t>
+          <t>111767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>224313</t>
+          <t>213771</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>212595</t>
+          <t>203324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>233372</t>
+          <t>223080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,32%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>30382</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21936</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>40516</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>22124</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15551</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>30728</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,13%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32888</t>
+          <t>22555</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23278</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43582</t>
+          <t>31196</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>55012</t>
+          <t>52937</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45199</t>
+          <t>42801</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67831</t>
+          <t>65461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>206824</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>196690</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>215270</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,19%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>168388</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>159784</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>174961</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>88,39%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,87%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>222147</t>
+          <t>161858</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>211453</t>
+          <t>153217</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>231757</t>
+          <t>168357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>390536</t>
+          <t>368682</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>377717</t>
+          <t>356158</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>400349</t>
+          <t>378818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,85%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5534</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17873</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11288</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6167</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18238</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>11328</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18060</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21855</t>
+          <t>21800</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31365</t>
+          <t>30967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157510</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>150110</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>162449</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,36%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>178297</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>171347</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>183418</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>94,05%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,38%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,75%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>174292</t>
+          <t>144876</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166799</t>
+          <t>138657</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179140</t>
+          <t>149547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>352590</t>
+          <t>302388</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>343080</t>
+          <t>293221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>360445</t>
+          <t>309025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167983</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167983</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167983</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>184859</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>184859</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184859</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374445</t>
+          <t>324188</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374445</t>
+          <t>324188</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374445</t>
+          <t>324188</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19284</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12763</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27793</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,39%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,41%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12000</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7479</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18401</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20268</t>
+          <t>12664</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13647</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28587</t>
+          <t>18842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>32268</t>
+          <t>31948</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23530</t>
+          <t>23018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42865</t>
+          <t>42048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>150092</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>141583</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>156613</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,61%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,59%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,46%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>154772</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>148371</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>159293</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,8%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>160970</t>
+          <t>153265</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152651</t>
+          <t>147087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167591</t>
+          <t>158365</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>315742</t>
+          <t>303357</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>305145</t>
+          <t>293257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>324480</t>
+          <t>312287</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>166772</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>166772</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>166772</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>165929</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>165929</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>165929</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>348010</t>
+          <t>335305</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>348010</t>
+          <t>335305</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348010</t>
+          <t>335305</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>79116</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>63956</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>94496</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>59719</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>47650</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>73478</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>60776</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67044</t>
+          <t>48839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99187</t>
+          <t>73096</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>139892</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123542</t>
+          <t>122247</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165872</t>
+          <t>161261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>621356</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>605976</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>636516</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>88,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>86,51%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,87%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>846</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>604431</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>590672</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>616500</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>91,01%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>88,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,83%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>678749</t>
+          <t>566841</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>662358</t>
+          <t>554521</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>694501</t>
+          <t>578778</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1283180</t>
+          <t>1188196</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1259823</t>
+          <t>1166827</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1302153</t>
+          <t>1205841</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700472</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700472</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700472</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664150</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664150</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664150</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761545</t>
+          <t>627617</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761545</t>
+          <t>627617</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761545</t>
+          <t>627617</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425695</t>
+          <t>1328088</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425695</t>
+          <t>1328088</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425695</t>
+          <t>1328088</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
